--- a/artifacts/traceability_reports/digital_ipos_vs_drs.xlsx
+++ b/artifacts/traceability_reports/digital_ipos_vs_drs.xlsx
@@ -13628,7 +13628,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05T14:20:59+00:00</t>
+          <t>2026-10-06T15:07:45+00:00</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\data\canonical\canonical_store.sqlite</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\data\canonical\canonical_store.sqlite</t>
         </is>
       </c>
     </row>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\artifacts\traceability_reports\digital_ipos_vs_drs.xlsx</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\artifacts\traceability_reports\digital_ipos_vs_drs.xlsx</t>
         </is>
       </c>
     </row>

--- a/artifacts/traceability_reports/digital_ipos_vs_drs.xlsx
+++ b/artifacts/traceability_reports/digital_ipos_vs_drs.xlsx
@@ -13628,7 +13628,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T15:07:45+00:00</t>
+          <t>2026-10-09T15:20:01+00:00</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>snap-b2e8101b00dc6909feaed885</t>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>b2e8101b00dc6909feaed8858c8391a595fd7fe52538e9b17b233477d99c8a6d</t>
+          <t>0c71eaa9e10d8478c2ac3726113d42cead2cf039a4bd64b4fab7e6c9dc116eac</t>
         </is>
       </c>
     </row>
